--- a/Test_cases-Magnus.xlsx
+++ b/Test_cases-Magnus.xlsx
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" s="1" thickBot="1">
@@ -1235,7 +1235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O52"/>
+  <dimension ref="B1:O53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.85546875" customWidth="1" style="1" min="1" max="1"/>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="O4" s="50" t="inlineStr">
         <is>
-          <t>Automated: test_invalid_password | Confirm on screen before submitting</t>
+          <t>Automated: test_invalid_password</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="C14" s="50" t="inlineStr">
         <is>
-          <t>TS_Magnus_04</t>
+          <t>TS_Magnus_03</t>
         </is>
       </c>
       <c r="D14" s="50" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="G14" s="50" t="inlineStr">
         <is>
-          <t>Create page opens from menu</t>
+          <t>Website link on Home page opens the correct site</t>
         </is>
       </c>
       <c r="H14" s="50" t="inlineStr">
@@ -2061,23 +2061,24 @@
       </c>
       <c r="I14" s="50" t="inlineStr">
         <is>
-          <t>1. Click Employee
-2. Click Create</t>
+          <t>1. Login
+2. On the Home page, read the link text at the end of the welcome message
+3. Click the link</t>
         </is>
       </c>
       <c r="J14" s="50" t="inlineStr">
         <is>
-          <t>Employee Create page opens</t>
+          <t>The site shown in the link text (http://jalatechnologies.com) opens</t>
         </is>
       </c>
       <c r="K14" s="50" t="inlineStr">
         <is>
-          <t>Working as expected</t>
+          <t>https://jalaacademy.com/ opens - link text and link address do not match</t>
         </is>
       </c>
       <c r="L14" s="50" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="M14" s="50" t="inlineStr">
@@ -2085,10 +2086,14 @@
           <t>Sahithi Dasari</t>
         </is>
       </c>
-      <c r="N14" s="50" t="inlineStr"/>
+      <c r="N14" s="50" t="inlineStr">
+        <is>
+          <t>DEF_01</t>
+        </is>
+      </c>
       <c r="O14" s="50" t="inlineStr">
         <is>
-          <t>Automated: test_create_page_opens_from_menu</t>
+          <t>Manual test</t>
         </is>
       </c>
     </row>
@@ -2118,15 +2123,82 @@
       </c>
       <c r="G15" s="50" t="inlineStr">
         <is>
+          <t>Create page opens from menu</t>
+        </is>
+      </c>
+      <c r="H15" s="50" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="I15" s="50" t="inlineStr">
+        <is>
+          <t>1. Click Employee
+2. Click Create</t>
+        </is>
+      </c>
+      <c r="J15" s="50" t="inlineStr">
+        <is>
+          <t>Employee Create page opens</t>
+        </is>
+      </c>
+      <c r="K15" s="50" t="inlineStr">
+        <is>
+          <t>Working as expected</t>
+        </is>
+      </c>
+      <c r="L15" s="50" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M15" s="50" t="inlineStr">
+        <is>
+          <t>Sahithi Dasari</t>
+        </is>
+      </c>
+      <c r="N15" s="50" t="n"/>
+      <c r="O15" s="50" t="inlineStr">
+        <is>
+          <t>Automated: test_create_page_opens_from_menu</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="50" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" s="50" t="inlineStr">
+        <is>
+          <t>TS_Magnus_04</t>
+        </is>
+      </c>
+      <c r="D16" s="50" t="inlineStr">
+        <is>
+          <t>TC_Magnus_14</t>
+        </is>
+      </c>
+      <c r="E16" s="50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F16" s="50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G16" s="50" t="inlineStr">
+        <is>
           <t>Create employee with all valid data</t>
         </is>
       </c>
-      <c r="H15" s="50" t="inlineStr">
+      <c r="H16" s="50" t="inlineStr">
         <is>
           <t>User is logged in; on Employee Create</t>
         </is>
       </c>
-      <c r="I15" s="50" t="inlineStr">
+      <c r="I16" s="50" t="inlineStr">
         <is>
           <t>1. Fill First/Last name, Email, Mobile
 2. Select Gender, Country
@@ -2135,213 +2207,142 @@
 Test data: Jalatest / Sahithi / jalatest.sahithi@gmail.com / 9XXXXXXXXX / F / India / QA-Automation</t>
         </is>
       </c>
-      <c r="J15" s="50" t="inlineStr">
+      <c r="J16" s="50" t="inlineStr">
         <is>
           <t>'Employee details saved successfully' shown; redirected to Search</t>
         </is>
       </c>
-      <c r="K15" s="50" t="inlineStr"/>
-      <c r="L15" s="50" t="inlineStr">
+      <c r="K16" s="50" t="n"/>
+      <c r="L16" s="50" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="M15" s="50" t="inlineStr"/>
-      <c r="N15" s="50" t="inlineStr"/>
-      <c r="O15" s="50" t="inlineStr">
+      <c r="M16" s="50" t="n"/>
+      <c r="N16" s="50" t="n"/>
+      <c r="O16" s="50" t="inlineStr">
         <is>
           <t>Automated: test_create_employee_success</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="50" t="n">
-        <v>14</v>
-      </c>
-      <c r="C16" s="50" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="50" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" s="50" t="inlineStr">
         <is>
           <t>TS_Magnus_04</t>
         </is>
       </c>
-      <c r="D16" s="50" t="inlineStr">
-        <is>
-          <t>TC_Magnus_14</t>
-        </is>
-      </c>
-      <c r="E16" s="50" t="inlineStr">
+      <c r="D17" s="50" t="inlineStr">
+        <is>
+          <t>TC_Magnus_15</t>
+        </is>
+      </c>
+      <c r="E17" s="50" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F16" s="50" t="inlineStr">
+      <c r="F17" s="50" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G16" s="50" t="inlineStr">
+      <c r="G17" s="50" t="inlineStr">
         <is>
           <t>Saved employee appears in search</t>
         </is>
       </c>
-      <c r="H16" s="50" t="inlineStr">
+      <c r="H17" s="50" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="I16" s="50" t="inlineStr">
+      <c r="I17" s="50" t="inlineStr">
         <is>
           <t>1. Create an employee
 2. Search by the new name
 Test data: Name used in previous case</t>
         </is>
       </c>
-      <c r="J16" s="50" t="inlineStr">
+      <c r="J17" s="50" t="inlineStr">
         <is>
           <t>The new employee is listed in the grid</t>
         </is>
       </c>
-      <c r="K16" s="50" t="inlineStr"/>
-      <c r="L16" s="50" t="inlineStr">
+      <c r="K17" s="50" t="n"/>
+      <c r="L17" s="50" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="M16" s="50" t="inlineStr"/>
-      <c r="N16" s="50" t="inlineStr"/>
-      <c r="O16" s="50" t="inlineStr">
+      <c r="M17" s="50" t="n"/>
+      <c r="N17" s="50" t="n"/>
+      <c r="O17" s="50" t="inlineStr">
         <is>
           <t>Manual test</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="50" t="n">
-        <v>15</v>
-      </c>
-      <c r="C17" s="50" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="50" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" s="50" t="inlineStr">
         <is>
           <t>TS_Magnus_04</t>
         </is>
       </c>
-      <c r="D17" s="50" t="inlineStr">
-        <is>
-          <t>TC_Magnus_15</t>
-        </is>
-      </c>
-      <c r="E17" s="50" t="inlineStr">
+      <c r="D18" s="50" t="inlineStr">
+        <is>
+          <t>TC_Magnus_16</t>
+        </is>
+      </c>
+      <c r="E18" s="50" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F17" s="50" t="inlineStr">
+      <c r="F18" s="50" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G17" s="50" t="inlineStr">
+      <c r="G18" s="50" t="inlineStr">
         <is>
           <t>Saved skills are kept after saving</t>
         </is>
       </c>
-      <c r="H17" s="50" t="inlineStr">
+      <c r="H18" s="50" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="I17" s="50" t="inlineStr">
+      <c r="I18" s="50" t="inlineStr">
         <is>
           <t>1. Create an employee with 2 skills ticked
 2. Search and click Edit
 Test data: AWS, DevOps</t>
         </is>
       </c>
-      <c r="J17" s="50" t="inlineStr">
+      <c r="J18" s="50" t="inlineStr">
         <is>
           <t>Both skills are still ticked on the Edit page</t>
         </is>
       </c>
-      <c r="K17" s="50" t="inlineStr">
-        <is>
-          <t>Not working as expected - see defect</t>
-        </is>
-      </c>
-      <c r="L17" s="50" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="M17" s="50" t="inlineStr">
-        <is>
-          <t>Sahithi Dasari</t>
-        </is>
-      </c>
-      <c r="N17" s="50" t="inlineStr">
-        <is>
-          <t>DEF_01</t>
-        </is>
-      </c>
-      <c r="O17" s="50" t="inlineStr">
-        <is>
-          <t>Manual test | Confirm on screen before submitting</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="50" t="n">
-        <v>16</v>
-      </c>
-      <c r="C18" s="50" t="inlineStr">
-        <is>
-          <t>TS_Magnus_05</t>
-        </is>
-      </c>
-      <c r="D18" s="50" t="inlineStr">
-        <is>
-          <t>TC_Magnus_16</t>
-        </is>
-      </c>
-      <c r="E18" s="50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F18" s="50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G18" s="50" t="inlineStr">
-        <is>
-          <t>Required field messages</t>
-        </is>
-      </c>
-      <c r="H18" s="50" t="inlineStr">
-        <is>
-          <t>User is logged in; on Employee Create</t>
-        </is>
-      </c>
-      <c r="I18" s="50" t="inlineStr">
-        <is>
-          <t>1. Leave all fields empty
-2. Click Save</t>
-        </is>
-      </c>
-      <c r="J18" s="50" t="inlineStr">
-        <is>
-          <t>Messages for first name, last name, email and mobile number</t>
-        </is>
-      </c>
-      <c r="K18" s="50" t="inlineStr"/>
+      <c r="K18" s="50" t="n"/>
       <c r="L18" s="50" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="M18" s="50" t="inlineStr"/>
-      <c r="N18" s="50" t="inlineStr"/>
+      <c r="M18" s="50" t="n"/>
+      <c r="N18" s="50" t="n"/>
       <c r="O18" s="50" t="inlineStr">
         <is>
-          <t>Automated: test_create_required_field_messages</t>
+          <t>Manual test</t>
         </is>
       </c>
     </row>
@@ -2371,15 +2372,74 @@
       </c>
       <c r="G19" s="50" t="inlineStr">
         <is>
+          <t>Required field messages</t>
+        </is>
+      </c>
+      <c r="H19" s="50" t="inlineStr">
+        <is>
+          <t>User is logged in; on Employee Create</t>
+        </is>
+      </c>
+      <c r="I19" s="50" t="inlineStr">
+        <is>
+          <t>1. Leave all fields empty
+2. Click Save</t>
+        </is>
+      </c>
+      <c r="J19" s="50" t="inlineStr">
+        <is>
+          <t>Messages for first name, last name, email and mobile number</t>
+        </is>
+      </c>
+      <c r="K19" s="50" t="n"/>
+      <c r="L19" s="50" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M19" s="50" t="n"/>
+      <c r="N19" s="50" t="n"/>
+      <c r="O19" s="50" t="inlineStr">
+        <is>
+          <t>Automated: test_create_required_field_messages</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="50" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" s="50" t="inlineStr">
+        <is>
+          <t>TS_Magnus_05</t>
+        </is>
+      </c>
+      <c r="D20" s="50" t="inlineStr">
+        <is>
+          <t>TC_Magnus_18</t>
+        </is>
+      </c>
+      <c r="E20" s="50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F20" s="50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G20" s="50" t="inlineStr">
+        <is>
           <t>Invalid email format</t>
         </is>
       </c>
-      <c r="H19" s="50" t="inlineStr">
+      <c r="H20" s="50" t="inlineStr">
         <is>
           <t>User is logged in; on Employee Create</t>
         </is>
       </c>
-      <c r="I19" s="50" t="inlineStr">
+      <c r="I20" s="50" t="inlineStr">
         <is>
           <t>1. Enter invalid email
 2. Fill other required fields
@@ -2387,213 +2447,142 @@
 Test data: wrong-email</t>
         </is>
       </c>
-      <c r="J19" s="50" t="inlineStr">
+      <c r="J20" s="50" t="inlineStr">
         <is>
           <t>'Please enter valid email address' shown</t>
         </is>
       </c>
-      <c r="K19" s="50" t="inlineStr"/>
-      <c r="L19" s="50" t="inlineStr">
+      <c r="K20" s="50" t="n"/>
+      <c r="L20" s="50" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="M19" s="50" t="inlineStr"/>
-      <c r="N19" s="50" t="inlineStr"/>
-      <c r="O19" s="50" t="inlineStr">
+      <c r="M20" s="50" t="n"/>
+      <c r="N20" s="50" t="n"/>
+      <c r="O20" s="50" t="inlineStr">
         <is>
           <t>Automated: test_create_invalid_email</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="50" t="n">
-        <v>18</v>
-      </c>
-      <c r="C20" s="50" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="50" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" s="50" t="inlineStr">
         <is>
           <t>TS_Magnus_05</t>
         </is>
       </c>
-      <c r="D20" s="50" t="inlineStr">
-        <is>
-          <t>TC_Magnus_18</t>
-        </is>
-      </c>
-      <c r="E20" s="50" t="inlineStr">
+      <c r="D21" s="50" t="inlineStr">
+        <is>
+          <t>TC_Magnus_19</t>
+        </is>
+      </c>
+      <c r="E21" s="50" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F20" s="50" t="inlineStr">
+      <c r="F21" s="50" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G20" s="50" t="inlineStr">
+      <c r="G21" s="50" t="inlineStr">
         <is>
           <t>Mobile number less than 10 digits</t>
         </is>
       </c>
-      <c r="H20" s="50" t="inlineStr">
+      <c r="H21" s="50" t="inlineStr">
         <is>
           <t>User is logged in; on Employee Create</t>
         </is>
       </c>
-      <c r="I20" s="50" t="inlineStr">
+      <c r="I21" s="50" t="inlineStr">
         <is>
           <t>1. Enter 5-digit mobile
 2. Click Save
 Test data: 12345</t>
         </is>
       </c>
-      <c r="J20" s="50" t="inlineStr">
+      <c r="J21" s="50" t="inlineStr">
         <is>
           <t>'Mobile No must be 10 digits.' shown</t>
         </is>
       </c>
-      <c r="K20" s="50" t="inlineStr"/>
-      <c r="L20" s="50" t="inlineStr">
+      <c r="K21" s="50" t="n"/>
+      <c r="L21" s="50" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="M20" s="50" t="inlineStr"/>
-      <c r="N20" s="50" t="inlineStr"/>
-      <c r="O20" s="50" t="inlineStr">
+      <c r="M21" s="50" t="n"/>
+      <c r="N21" s="50" t="n"/>
+      <c r="O21" s="50" t="inlineStr">
         <is>
           <t>Automated: test_create_mobile_must_be_10_digits</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="C21" s="50" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="50" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" s="50" t="inlineStr">
         <is>
           <t>TS_Magnus_05</t>
         </is>
       </c>
-      <c r="D21" s="50" t="inlineStr">
-        <is>
-          <t>TC_Magnus_19</t>
-        </is>
-      </c>
-      <c r="E21" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F21" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G21" s="50" t="inlineStr">
+      <c r="D22" s="50" t="inlineStr">
+        <is>
+          <t>TC_Magnus_20</t>
+        </is>
+      </c>
+      <c r="E22" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F22" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G22" s="50" t="inlineStr">
         <is>
           <t>Mobile number accepts letters?</t>
         </is>
       </c>
-      <c r="H21" s="50" t="inlineStr">
+      <c r="H22" s="50" t="inlineStr">
         <is>
           <t>User is logged in; on Employee Create</t>
         </is>
       </c>
-      <c r="I21" s="50" t="inlineStr">
+      <c r="I22" s="50" t="inlineStr">
         <is>
           <t>1. Enter letters in Mobile
 2. Click Save
 Test data: abcdefghij</t>
         </is>
       </c>
-      <c r="J21" s="50" t="inlineStr">
+      <c r="J22" s="50" t="inlineStr">
         <is>
           <t>Validation error - only digits allowed</t>
         </is>
       </c>
-      <c r="K21" s="50" t="inlineStr"/>
-      <c r="L21" s="50" t="inlineStr">
+      <c r="K22" s="50" t="n"/>
+      <c r="L22" s="50" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="M21" s="50" t="inlineStr"/>
-      <c r="N21" s="50" t="inlineStr"/>
-      <c r="O21" s="50" t="inlineStr">
+      <c r="M22" s="50" t="n"/>
+      <c r="N22" s="50" t="n"/>
+      <c r="O22" s="50" t="inlineStr">
         <is>
           <t>Manual test</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="50" t="n">
-        <v>20</v>
-      </c>
-      <c r="C22" s="50" t="inlineStr">
-        <is>
-          <t>TS_Magnus_05</t>
-        </is>
-      </c>
-      <c r="D22" s="50" t="inlineStr">
-        <is>
-          <t>TC_Magnus_20</t>
-        </is>
-      </c>
-      <c r="E22" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F22" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G22" s="50" t="inlineStr">
-        <is>
-          <t>First name max length 20</t>
-        </is>
-      </c>
-      <c r="H22" s="50" t="inlineStr">
-        <is>
-          <t>User is logged in; on Employee Create</t>
-        </is>
-      </c>
-      <c r="I22" s="50" t="inlineStr">
-        <is>
-          <t>1. Type 30 characters in First Name
-Test data: AAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
-        </is>
-      </c>
-      <c r="J22" s="50" t="inlineStr">
-        <is>
-          <t>Only 20 characters are accepted</t>
-        </is>
-      </c>
-      <c r="K22" s="50" t="inlineStr">
-        <is>
-          <t>Not working as expected - see defect</t>
-        </is>
-      </c>
-      <c r="L22" s="50" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="M22" s="50" t="inlineStr">
-        <is>
-          <t>Sahithi Dasari</t>
-        </is>
-      </c>
-      <c r="N22" s="50" t="inlineStr">
-        <is>
-          <t>DEF_05</t>
-        </is>
-      </c>
-      <c r="O22" s="50" t="inlineStr">
-        <is>
-          <t>Automated: test_create_name_max_length_20 | Confirm on screen before submitting</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2592,7 @@
       </c>
       <c r="C23" s="50" t="inlineStr">
         <is>
-          <t>TS_Magnus_06</t>
+          <t>TS_Magnus_05</t>
         </is>
       </c>
       <c r="D23" s="50" t="inlineStr">
@@ -2623,7 +2612,7 @@
       </c>
       <c r="G23" s="50" t="inlineStr">
         <is>
-          <t>Default values on the form</t>
+          <t>First name max length 20</t>
         </is>
       </c>
       <c r="H23" s="50" t="inlineStr">
@@ -2633,25 +2622,38 @@
       </c>
       <c r="I23" s="50" t="inlineStr">
         <is>
-          <t>1. Open the page and check defaults</t>
+          <t>1. Type 30 characters in First Name
+Test data: AAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
         </is>
       </c>
       <c r="J23" s="50" t="inlineStr">
         <is>
-          <t>Male selected; Country '--Select Country--'; Other City box hidden</t>
-        </is>
-      </c>
-      <c r="K23" s="50" t="inlineStr"/>
+          <t>Only 20 characters are accepted</t>
+        </is>
+      </c>
+      <c r="K23" s="50" t="inlineStr">
+        <is>
+          <t>Not working as expected - see defect</t>
+        </is>
+      </c>
       <c r="L23" s="50" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M23" s="50" t="inlineStr"/>
-      <c r="N23" s="50" t="inlineStr"/>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="M23" s="50" t="inlineStr">
+        <is>
+          <t>Sahithi Dasari</t>
+        </is>
+      </c>
+      <c r="N23" s="50" t="inlineStr">
+        <is>
+          <t>DEF_05</t>
+        </is>
+      </c>
       <c r="O23" s="50" t="inlineStr">
         <is>
-          <t>Automated: test_create_page_default_values</t>
+          <t>Automated: test_create_name_max_length_20</t>
         </is>
       </c>
     </row>
@@ -2681,95 +2683,95 @@
       </c>
       <c r="G24" s="50" t="inlineStr">
         <is>
+          <t>Default values on the form</t>
+        </is>
+      </c>
+      <c r="H24" s="50" t="inlineStr">
+        <is>
+          <t>User is logged in; on Employee Create</t>
+        </is>
+      </c>
+      <c r="I24" s="50" t="inlineStr">
+        <is>
+          <t>1. Open the page and check defaults</t>
+        </is>
+      </c>
+      <c r="J24" s="50" t="inlineStr">
+        <is>
+          <t>Male selected; Country '--Select Country--'; Other City box hidden</t>
+        </is>
+      </c>
+      <c r="K24" s="50" t="n"/>
+      <c r="L24" s="50" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M24" s="50" t="n"/>
+      <c r="N24" s="50" t="n"/>
+      <c r="O24" s="50" t="inlineStr">
+        <is>
+          <t>Automated: test_create_page_default_values</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="50" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" s="50" t="inlineStr">
+        <is>
+          <t>TS_Magnus_06</t>
+        </is>
+      </c>
+      <c r="D25" s="50" t="inlineStr">
+        <is>
+          <t>TC_Magnus_23</t>
+        </is>
+      </c>
+      <c r="E25" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F25" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G25" s="50" t="inlineStr">
+        <is>
           <t>Country loads its cities</t>
         </is>
       </c>
-      <c r="H24" s="50" t="inlineStr">
+      <c r="H25" s="50" t="inlineStr">
         <is>
           <t>User is logged in; on Employee Create</t>
         </is>
       </c>
-      <c r="I24" s="50" t="inlineStr">
+      <c r="I25" s="50" t="inlineStr">
         <is>
           <t>1. Select a country
 2. Open City dropdown
 Test data: India</t>
         </is>
       </c>
-      <c r="J24" s="50" t="inlineStr">
+      <c r="J25" s="50" t="inlineStr">
         <is>
           <t>City dropdown lists cities of India</t>
         </is>
       </c>
-      <c r="K24" s="50" t="inlineStr"/>
-      <c r="L24" s="50" t="inlineStr">
+      <c r="K25" s="50" t="n"/>
+      <c r="L25" s="50" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="M24" s="50" t="inlineStr"/>
-      <c r="N24" s="50" t="inlineStr"/>
-      <c r="O24" s="50" t="inlineStr">
+      <c r="M25" s="50" t="n"/>
+      <c r="N25" s="50" t="n"/>
+      <c r="O25" s="50" t="inlineStr">
         <is>
           <t>Automated: test_country_loads_cities</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="50" t="n">
-        <v>23</v>
-      </c>
-      <c r="C25" s="50" t="inlineStr">
-        <is>
-          <t>TS_Magnus_06</t>
-        </is>
-      </c>
-      <c r="D25" s="50" t="inlineStr">
-        <is>
-          <t>TC_Magnus_23</t>
-        </is>
-      </c>
-      <c r="E25" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F25" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G25" s="50" t="inlineStr">
-        <is>
-          <t>Other City checkbox</t>
-        </is>
-      </c>
-      <c r="H25" s="50" t="inlineStr">
-        <is>
-          <t>User is logged in; on Employee Create</t>
-        </is>
-      </c>
-      <c r="I25" s="50" t="inlineStr">
-        <is>
-          <t>1. Tick Other City</t>
-        </is>
-      </c>
-      <c r="J25" s="50" t="inlineStr">
-        <is>
-          <t>Other City text box shown; City dropdown disabled</t>
-        </is>
-      </c>
-      <c r="K25" s="50" t="inlineStr"/>
-      <c r="L25" s="50" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M25" s="50" t="inlineStr"/>
-      <c r="N25" s="50" t="inlineStr"/>
-      <c r="O25" s="50" t="inlineStr">
-        <is>
-          <t>Automated: test_other_city_checkbox</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2801,7 @@
       </c>
       <c r="G26" s="50" t="inlineStr">
         <is>
-          <t>Skill checkboxes listed</t>
+          <t>Other City checkbox</t>
         </is>
       </c>
       <c r="H26" s="50" t="inlineStr">
@@ -2809,37 +2811,25 @@
       </c>
       <c r="I26" s="50" t="inlineStr">
         <is>
-          <t>1. Check the Skills section</t>
+          <t>1. Tick Other City</t>
         </is>
       </c>
       <c r="J26" s="50" t="inlineStr">
         <is>
-          <t>6 skills: AWS, DevOps, Full Stack Developer, Middleware, QA-Automation, WebServices</t>
-        </is>
-      </c>
-      <c r="K26" s="50" t="inlineStr">
-        <is>
-          <t>Not working as expected - see defect</t>
-        </is>
-      </c>
+          <t>Other City text box shown; City dropdown disabled</t>
+        </is>
+      </c>
+      <c r="K26" s="50" t="n"/>
       <c r="L26" s="50" t="inlineStr">
         <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="M26" s="50" t="inlineStr">
-        <is>
-          <t>Sahithi Dasari</t>
-        </is>
-      </c>
-      <c r="N26" s="50" t="inlineStr">
-        <is>
-          <t>DEF_04</t>
-        </is>
-      </c>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M26" s="50" t="n"/>
+      <c r="N26" s="50" t="n"/>
       <c r="O26" s="50" t="inlineStr">
         <is>
-          <t>Automated: test_skill_checkboxes_listed | Confirm on screen before submitting</t>
+          <t>Automated: test_other_city_checkbox</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2859,7 @@
       </c>
       <c r="G27" s="50" t="inlineStr">
         <is>
-          <t>Cancel button</t>
+          <t>Skill checkboxes listed</t>
         </is>
       </c>
       <c r="H27" s="50" t="inlineStr">
@@ -2879,26 +2869,37 @@
       </c>
       <c r="I27" s="50" t="inlineStr">
         <is>
-          <t>1. Enter some data
-2. Click Cancel</t>
+          <t>1. Check the Skills section</t>
         </is>
       </c>
       <c r="J27" s="50" t="inlineStr">
         <is>
-          <t>Search page opens, nothing saved</t>
-        </is>
-      </c>
-      <c r="K27" s="50" t="inlineStr"/>
+          <t>6 skills: AWS, DevOps, Full Stack Developer, Middleware, QA-Automation, WebServices</t>
+        </is>
+      </c>
+      <c r="K27" s="50" t="inlineStr">
+        <is>
+          <t>Not working as expected - see defect</t>
+        </is>
+      </c>
       <c r="L27" s="50" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M27" s="50" t="inlineStr"/>
-      <c r="N27" s="50" t="inlineStr"/>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="M27" s="50" t="inlineStr">
+        <is>
+          <t>Sahithi Dasari</t>
+        </is>
+      </c>
+      <c r="N27" s="50" t="inlineStr">
+        <is>
+          <t>DEF_04</t>
+        </is>
+      </c>
       <c r="O27" s="50" t="inlineStr">
         <is>
-          <t>Manual test</t>
+          <t>Automated: test_skill_checkboxes_listed</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2909,7 @@
       </c>
       <c r="C28" s="50" t="inlineStr">
         <is>
-          <t>TS_Magnus_07</t>
+          <t>TS_Magnus_06</t>
         </is>
       </c>
       <c r="D28" s="50" t="inlineStr">
@@ -2918,54 +2919,46 @@
       </c>
       <c r="E28" s="50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F28" s="50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G28" s="50" t="inlineStr">
         <is>
-          <t>Search page opens from menu</t>
+          <t>Cancel button</t>
         </is>
       </c>
       <c r="H28" s="50" t="inlineStr">
         <is>
-          <t>User is logged in</t>
+          <t>User is logged in; on Employee Create</t>
         </is>
       </c>
       <c r="I28" s="50" t="inlineStr">
         <is>
-          <t>1. Click Employee
-2. Click Search</t>
+          <t>1. Enter some data
+2. Click Cancel</t>
         </is>
       </c>
       <c r="J28" s="50" t="inlineStr">
         <is>
-          <t>Employee Search page opens with the grid</t>
-        </is>
-      </c>
-      <c r="K28" s="50" t="inlineStr">
-        <is>
-          <t>Working as expected</t>
-        </is>
-      </c>
+          <t>Search page opens, nothing saved</t>
+        </is>
+      </c>
+      <c r="K28" s="50" t="n"/>
       <c r="L28" s="50" t="inlineStr">
         <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="M28" s="50" t="inlineStr">
-        <is>
-          <t>Sahithi Dasari</t>
-        </is>
-      </c>
-      <c r="N28" s="50" t="inlineStr"/>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M28" s="50" t="n"/>
+      <c r="N28" s="50" t="n"/>
       <c r="O28" s="50" t="inlineStr">
         <is>
-          <t>Automated: test_search_page_opens_from_menu</t>
+          <t>Manual test</t>
         </is>
       </c>
     </row>
@@ -2985,45 +2978,54 @@
       </c>
       <c r="E29" s="50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F29" s="50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G29" s="50" t="inlineStr">
         <is>
-          <t>Grid column headers</t>
+          <t>Search page opens from menu</t>
         </is>
       </c>
       <c r="H29" s="50" t="inlineStr">
         <is>
-          <t>User is logged in; on Employee Search</t>
+          <t>User is logged in</t>
         </is>
       </c>
       <c r="I29" s="50" t="inlineStr">
         <is>
-          <t>1. Check the table headers</t>
+          <t>1. Click Employee
+2. Click Search</t>
         </is>
       </c>
       <c r="J29" s="50" t="inlineStr">
         <is>
-          <t>First Name, Last Name, Mobile No, Email Id, Gender, Birth Date, Country, City, Action</t>
-        </is>
-      </c>
-      <c r="K29" s="50" t="inlineStr"/>
+          <t>Employee Search page opens with the grid</t>
+        </is>
+      </c>
+      <c r="K29" s="50" t="inlineStr">
+        <is>
+          <t>Working as expected</t>
+        </is>
+      </c>
       <c r="L29" s="50" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M29" s="50" t="inlineStr"/>
-      <c r="N29" s="50" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M29" s="50" t="inlineStr">
+        <is>
+          <t>Sahithi Dasari</t>
+        </is>
+      </c>
+      <c r="N29" s="50" t="n"/>
       <c r="O29" s="50" t="inlineStr">
         <is>
-          <t>Automated: test_search_table_headers</t>
+          <t>Automated: test_search_page_opens_from_menu</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3055,7 @@
       </c>
       <c r="G30" s="50" t="inlineStr">
         <is>
-          <t>10 records per page</t>
+          <t>Grid column headers</t>
         </is>
       </c>
       <c r="H30" s="50" t="inlineStr">
@@ -3063,25 +3065,25 @@
       </c>
       <c r="I30" s="50" t="inlineStr">
         <is>
-          <t>1. Count rows on page 1</t>
+          <t>1. Check the table headers</t>
         </is>
       </c>
       <c r="J30" s="50" t="inlineStr">
         <is>
-          <t>10 rows shown</t>
-        </is>
-      </c>
-      <c r="K30" s="50" t="inlineStr"/>
+          <t>First Name, Last Name, Mobile No, Email Id, Gender, Birth Date, Country, City, Action</t>
+        </is>
+      </c>
+      <c r="K30" s="50" t="n"/>
       <c r="L30" s="50" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="M30" s="50" t="inlineStr"/>
-      <c r="N30" s="50" t="inlineStr"/>
+      <c r="M30" s="50" t="n"/>
+      <c r="N30" s="50" t="n"/>
       <c r="O30" s="50" t="inlineStr">
         <is>
-          <t>Automated: test_search_shows_10_rows_per_page</t>
+          <t>Automated: test_search_table_headers</t>
         </is>
       </c>
     </row>
@@ -3101,345 +3103,345 @@
       </c>
       <c r="E31" s="50" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F31" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G31" s="50" t="inlineStr">
+        <is>
+          <t>10 records per page</t>
+        </is>
+      </c>
+      <c r="H31" s="50" t="inlineStr">
+        <is>
+          <t>User is logged in; on Employee Search</t>
+        </is>
+      </c>
+      <c r="I31" s="50" t="inlineStr">
+        <is>
+          <t>1. Count rows on page 1</t>
+        </is>
+      </c>
+      <c r="J31" s="50" t="inlineStr">
+        <is>
+          <t>10 rows shown</t>
+        </is>
+      </c>
+      <c r="K31" s="50" t="n"/>
+      <c r="L31" s="50" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M31" s="50" t="n"/>
+      <c r="N31" s="50" t="n"/>
+      <c r="O31" s="50" t="inlineStr">
+        <is>
+          <t>Automated: test_search_shows_10_rows_per_page</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="50" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" s="50" t="inlineStr">
+        <is>
+          <t>TS_Magnus_07</t>
+        </is>
+      </c>
+      <c r="D32" s="50" t="inlineStr">
+        <is>
+          <t>TC_Magnus_30</t>
+        </is>
+      </c>
+      <c r="E32" s="50" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F31" s="50" t="inlineStr">
+      <c r="F32" s="50" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G31" s="50" t="inlineStr">
+      <c r="G32" s="50" t="inlineStr">
         <is>
           <t>Search by name</t>
         </is>
       </c>
-      <c r="H31" s="50" t="inlineStr">
+      <c r="H32" s="50" t="inlineStr">
         <is>
           <t>User is logged in; on Employee Search</t>
         </is>
       </c>
-      <c r="I31" s="50" t="inlineStr">
+      <c r="I32" s="50" t="inlineStr">
         <is>
           <t>1. Enter a name
 2. Click Search
 Test data: First name from row 1</t>
         </is>
       </c>
-      <c r="J31" s="50" t="inlineStr">
+      <c r="J32" s="50" t="inlineStr">
         <is>
           <t>Only matching employees shown</t>
         </is>
       </c>
-      <c r="K31" s="50" t="inlineStr"/>
-      <c r="L31" s="50" t="inlineStr">
+      <c r="K32" s="50" t="n"/>
+      <c r="L32" s="50" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="M31" s="50" t="inlineStr"/>
-      <c r="N31" s="50" t="inlineStr"/>
-      <c r="O31" s="50" t="inlineStr">
+      <c r="M32" s="50" t="n"/>
+      <c r="N32" s="50" t="n"/>
+      <c r="O32" s="50" t="inlineStr">
         <is>
           <t>Automated: test_search_by_name</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="50" t="n">
-        <v>30</v>
-      </c>
-      <c r="C32" s="50" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="50" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" s="50" t="inlineStr">
         <is>
           <t>TS_Magnus_07</t>
         </is>
       </c>
-      <c r="D32" s="50" t="inlineStr">
-        <is>
-          <t>TC_Magnus_30</t>
-        </is>
-      </c>
-      <c r="E32" s="50" t="inlineStr">
+      <c r="D33" s="50" t="inlineStr">
+        <is>
+          <t>TC_Magnus_31</t>
+        </is>
+      </c>
+      <c r="E33" s="50" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F32" s="50" t="inlineStr">
+      <c r="F33" s="50" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G32" s="50" t="inlineStr">
+      <c r="G33" s="50" t="inlineStr">
         <is>
           <t>Search by mobile number</t>
         </is>
       </c>
-      <c r="H32" s="50" t="inlineStr">
+      <c r="H33" s="50" t="inlineStr">
         <is>
           <t>User is logged in; on Employee Search</t>
         </is>
       </c>
-      <c r="I32" s="50" t="inlineStr">
+      <c r="I33" s="50" t="inlineStr">
         <is>
           <t>1. Enter a mobile number
 2. Click Search
 Test data: Mobile from row 1</t>
         </is>
       </c>
-      <c r="J32" s="50" t="inlineStr">
+      <c r="J33" s="50" t="inlineStr">
         <is>
           <t>Matching employee shown</t>
         </is>
       </c>
-      <c r="K32" s="50" t="inlineStr"/>
-      <c r="L32" s="50" t="inlineStr">
+      <c r="K33" s="50" t="n"/>
+      <c r="L33" s="50" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="M32" s="50" t="inlineStr"/>
-      <c r="N32" s="50" t="inlineStr"/>
-      <c r="O32" s="50" t="inlineStr">
+      <c r="M33" s="50" t="n"/>
+      <c r="N33" s="50" t="n"/>
+      <c r="O33" s="50" t="inlineStr">
         <is>
           <t>Automated: test_search_by_mobile</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="50" t="n">
-        <v>31</v>
-      </c>
-      <c r="C33" s="50" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="50" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" s="50" t="inlineStr">
         <is>
           <t>TS_Magnus_07</t>
         </is>
       </c>
-      <c r="D33" s="50" t="inlineStr">
-        <is>
-          <t>TC_Magnus_31</t>
-        </is>
-      </c>
-      <c r="E33" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F33" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G33" s="50" t="inlineStr">
+      <c r="D34" s="50" t="inlineStr">
+        <is>
+          <t>TC_Magnus_32</t>
+        </is>
+      </c>
+      <c r="E34" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F34" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G34" s="50" t="inlineStr">
         <is>
           <t>Search with no match</t>
         </is>
       </c>
-      <c r="H33" s="50" t="inlineStr">
+      <c r="H34" s="50" t="inlineStr">
         <is>
           <t>User is logged in; on Employee Search</t>
         </is>
       </c>
-      <c r="I33" s="50" t="inlineStr">
+      <c r="I34" s="50" t="inlineStr">
         <is>
           <t>1. Enter a name that does not exist
 2. Click Search
 Test data: zzqqxx_no_such_name</t>
         </is>
       </c>
-      <c r="J33" s="50" t="inlineStr">
+      <c r="J34" s="50" t="inlineStr">
         <is>
           <t>No records / 'No data available' shown</t>
         </is>
       </c>
-      <c r="K33" s="50" t="inlineStr"/>
-      <c r="L33" s="50" t="inlineStr">
+      <c r="K34" s="50" t="n"/>
+      <c r="L34" s="50" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="M33" s="50" t="inlineStr"/>
-      <c r="N33" s="50" t="inlineStr"/>
-      <c r="O33" s="50" t="inlineStr">
+      <c r="M34" s="50" t="n"/>
+      <c r="N34" s="50" t="n"/>
+      <c r="O34" s="50" t="inlineStr">
         <is>
           <t>Automated: test_search_no_results</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="50" t="n">
-        <v>32</v>
-      </c>
-      <c r="C34" s="50" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="50" t="n">
+        <v>33</v>
+      </c>
+      <c r="C35" s="50" t="inlineStr">
         <is>
           <t>TS_Magnus_07</t>
         </is>
       </c>
-      <c r="D34" s="50" t="inlineStr">
-        <is>
-          <t>TC_Magnus_32</t>
-        </is>
-      </c>
-      <c r="E34" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F34" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G34" s="50" t="inlineStr">
+      <c r="D35" s="50" t="inlineStr">
+        <is>
+          <t>TC_Magnus_33</t>
+        </is>
+      </c>
+      <c r="E35" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F35" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G35" s="50" t="inlineStr">
         <is>
           <t>Search by pressing Enter</t>
         </is>
       </c>
-      <c r="H34" s="50" t="inlineStr">
+      <c r="H35" s="50" t="inlineStr">
         <is>
           <t>User is logged in; on Employee Search</t>
         </is>
       </c>
-      <c r="I34" s="50" t="inlineStr">
+      <c r="I35" s="50" t="inlineStr">
         <is>
           <t>1. Type a name
 2. Press Enter
 Test data: Any name</t>
         </is>
       </c>
-      <c r="J34" s="50" t="inlineStr">
+      <c r="J35" s="50" t="inlineStr">
         <is>
           <t>Search runs without clicking the button</t>
         </is>
       </c>
-      <c r="K34" s="50" t="inlineStr"/>
-      <c r="L34" s="50" t="inlineStr">
+      <c r="K35" s="50" t="n"/>
+      <c r="L35" s="50" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="M34" s="50" t="inlineStr"/>
-      <c r="N34" s="50" t="inlineStr"/>
-      <c r="O34" s="50" t="inlineStr">
+      <c r="M35" s="50" t="n"/>
+      <c r="N35" s="50" t="n"/>
+      <c r="O35" s="50" t="inlineStr">
         <is>
           <t>Automated: ex5_misc_scenarios.py (actions)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="50" t="n">
-        <v>33</v>
-      </c>
-      <c r="C35" s="50" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="50" t="n">
+        <v>34</v>
+      </c>
+      <c r="C36" s="50" t="inlineStr">
         <is>
           <t>TS_Magnus_08</t>
         </is>
       </c>
-      <c r="D35" s="50" t="inlineStr">
-        <is>
-          <t>TC_Magnus_33</t>
-        </is>
-      </c>
-      <c r="E35" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F35" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G35" s="50" t="inlineStr">
+      <c r="D36" s="50" t="inlineStr">
+        <is>
+          <t>TC_Magnus_34</t>
+        </is>
+      </c>
+      <c r="E36" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F36" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G36" s="50" t="inlineStr">
         <is>
           <t>Clear button</t>
         </is>
       </c>
-      <c r="H35" s="50" t="inlineStr">
+      <c r="H36" s="50" t="inlineStr">
         <is>
           <t>User is logged in; on Employee Search</t>
         </is>
       </c>
-      <c r="I35" s="50" t="inlineStr">
+      <c r="I36" s="50" t="inlineStr">
         <is>
           <t>1. Type a name
 2. Click Clear
 Test data: abc</t>
         </is>
       </c>
-      <c r="J35" s="50" t="inlineStr">
+      <c r="J36" s="50" t="inlineStr">
         <is>
           <t>Search boxes emptied, full list shown</t>
         </is>
       </c>
-      <c r="K35" s="50" t="inlineStr"/>
-      <c r="L35" s="50" t="inlineStr">
+      <c r="K36" s="50" t="n"/>
+      <c r="L36" s="50" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="M35" s="50" t="inlineStr"/>
-      <c r="N35" s="50" t="inlineStr"/>
-      <c r="O35" s="50" t="inlineStr">
+      <c r="M36" s="50" t="n"/>
+      <c r="N36" s="50" t="n"/>
+      <c r="O36" s="50" t="inlineStr">
         <is>
           <t>Automated: test_clear_button</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="50" t="n">
-        <v>34</v>
-      </c>
-      <c r="C36" s="50" t="inlineStr">
-        <is>
-          <t>TS_Magnus_08</t>
-        </is>
-      </c>
-      <c r="D36" s="50" t="inlineStr">
-        <is>
-          <t>TC_Magnus_34</t>
-        </is>
-      </c>
-      <c r="E36" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F36" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G36" s="50" t="inlineStr">
-        <is>
-          <t>Pagination Next</t>
-        </is>
-      </c>
-      <c r="H36" s="50" t="inlineStr">
-        <is>
-          <t>User is logged in; on Employee Search</t>
-        </is>
-      </c>
-      <c r="I36" s="50" t="inlineStr">
-        <is>
-          <t>1. Click Next</t>
-        </is>
-      </c>
-      <c r="J36" s="50" t="inlineStr">
-        <is>
-          <t>Page 2 shows different employees</t>
-        </is>
-      </c>
-      <c r="K36" s="50" t="inlineStr"/>
-      <c r="L36" s="50" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M36" s="50" t="inlineStr"/>
-      <c r="N36" s="50" t="inlineStr"/>
-      <c r="O36" s="50" t="inlineStr">
-        <is>
-          <t>Automated: test_pagination_next</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3471,7 @@
       </c>
       <c r="G37" s="50" t="inlineStr">
         <is>
-          <t>Add Employee button</t>
+          <t>Pagination Next</t>
         </is>
       </c>
       <c r="H37" s="50" t="inlineStr">
@@ -3479,25 +3481,25 @@
       </c>
       <c r="I37" s="50" t="inlineStr">
         <is>
-          <t>1. Click Add Employee</t>
+          <t>1. Click Next</t>
         </is>
       </c>
       <c r="J37" s="50" t="inlineStr">
         <is>
-          <t>Employee Create page opens</t>
-        </is>
-      </c>
-      <c r="K37" s="50" t="inlineStr"/>
+          <t>Page 2 shows different employees</t>
+        </is>
+      </c>
+      <c r="K37" s="50" t="n"/>
       <c r="L37" s="50" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="M37" s="50" t="inlineStr"/>
-      <c r="N37" s="50" t="inlineStr"/>
+      <c r="M37" s="50" t="n"/>
+      <c r="N37" s="50" t="n"/>
       <c r="O37" s="50" t="inlineStr">
         <is>
-          <t>Automated: test_add_employee_button</t>
+          <t>Automated: test_pagination_next</t>
         </is>
       </c>
     </row>
@@ -3517,17 +3519,17 @@
       </c>
       <c r="E38" s="50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F38" s="50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G38" s="50" t="inlineStr">
         <is>
-          <t>Delete asks for confirmation</t>
+          <t>Add Employee button</t>
         </is>
       </c>
       <c r="H38" s="50" t="inlineStr">
@@ -3537,26 +3539,25 @@
       </c>
       <c r="I38" s="50" t="inlineStr">
         <is>
-          <t>1. Click Delete on a row
-2. Click Cancel</t>
+          <t>1. Click Add Employee</t>
         </is>
       </c>
       <c r="J38" s="50" t="inlineStr">
         <is>
-          <t>'Are you sure you want to delete?' popup; record NOT deleted after Cancel</t>
-        </is>
-      </c>
-      <c r="K38" s="50" t="inlineStr"/>
+          <t>Employee Create page opens</t>
+        </is>
+      </c>
+      <c r="K38" s="50" t="n"/>
       <c r="L38" s="50" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="M38" s="50" t="inlineStr"/>
-      <c r="N38" s="50" t="inlineStr"/>
+      <c r="M38" s="50" t="n"/>
+      <c r="N38" s="50" t="n"/>
       <c r="O38" s="50" t="inlineStr">
         <is>
-          <t>Automated: test_delete_asks_for_confirmation</t>
+          <t>Automated: test_add_employee_button</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3567,7 @@
       </c>
       <c r="C39" s="50" t="inlineStr">
         <is>
-          <t>TS_Magnus_09</t>
+          <t>TS_Magnus_08</t>
         </is>
       </c>
       <c r="D39" s="50" t="inlineStr">
@@ -3576,46 +3577,46 @@
       </c>
       <c r="E39" s="50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F39" s="50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G39" s="50" t="inlineStr">
         <is>
-          <t>Multiple Tabs switch content</t>
+          <t>Delete asks for confirmation</t>
         </is>
       </c>
       <c r="H39" s="50" t="inlineStr">
         <is>
-          <t>User is logged in</t>
+          <t>User is logged in; on Employee Search</t>
         </is>
       </c>
       <c r="I39" s="50" t="inlineStr">
         <is>
-          <t>1. Open More &gt; Multiple Tabs
-2. Click 'UnLearning'</t>
+          <t>1. Click Delete on a row
+2. Click Cancel</t>
         </is>
       </c>
       <c r="J39" s="50" t="inlineStr">
         <is>
-          <t>UnLearning content shown, first tab hidden</t>
-        </is>
-      </c>
-      <c r="K39" s="50" t="inlineStr"/>
+          <t>'Are you sure you want to delete?' popup; record NOT deleted after Cancel</t>
+        </is>
+      </c>
+      <c r="K39" s="50" t="n"/>
       <c r="L39" s="50" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="M39" s="50" t="inlineStr"/>
-      <c r="N39" s="50" t="inlineStr"/>
+      <c r="M39" s="50" t="n"/>
+      <c r="N39" s="50" t="n"/>
       <c r="O39" s="50" t="inlineStr">
         <is>
-          <t>Automated: test_tabs_switch_content</t>
+          <t>Automated: test_delete_asks_for_confirmation</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3646,7 @@
       </c>
       <c r="G40" s="50" t="inlineStr">
         <is>
-          <t>Single menu message</t>
+          <t>Multiple Tabs switch content</t>
         </is>
       </c>
       <c r="H40" s="50" t="inlineStr">
@@ -3655,38 +3656,26 @@
       </c>
       <c r="I40" s="50" t="inlineStr">
         <is>
-          <t>1. Open More &gt; Menu
-2. Click Java</t>
+          <t>1. Open More &gt; Multiple Tabs
+2. Click 'UnLearning'</t>
         </is>
       </c>
       <c r="J40" s="50" t="inlineStr">
         <is>
-          <t>'You Have Selected Java Menu Option.'</t>
-        </is>
-      </c>
-      <c r="K40" s="50" t="inlineStr">
-        <is>
-          <t>Not working as expected - see defect</t>
-        </is>
-      </c>
+          <t>UnLearning content shown, first tab hidden</t>
+        </is>
+      </c>
+      <c r="K40" s="50" t="n"/>
       <c r="L40" s="50" t="inlineStr">
         <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="M40" s="50" t="inlineStr">
-        <is>
-          <t>Sahithi Dasari</t>
-        </is>
-      </c>
-      <c r="N40" s="50" t="inlineStr">
-        <is>
-          <t>DEF_02</t>
-        </is>
-      </c>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M40" s="50" t="n"/>
+      <c r="N40" s="50" t="n"/>
       <c r="O40" s="50" t="inlineStr">
         <is>
-          <t>Automated: test_menu_single_option_message | Confirm on screen before submitting</t>
+          <t>Automated: test_tabs_switch_content</t>
         </is>
       </c>
     </row>
@@ -3716,168 +3705,168 @@
       </c>
       <c r="G41" s="50" t="inlineStr">
         <is>
+          <t>Single menu message</t>
+        </is>
+      </c>
+      <c r="H41" s="50" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="I41" s="50" t="inlineStr">
+        <is>
+          <t>1. Open More &gt; Menu
+2. Click Java</t>
+        </is>
+      </c>
+      <c r="J41" s="50" t="inlineStr">
+        <is>
+          <t>'You Have Selected Java Menu Option.'</t>
+        </is>
+      </c>
+      <c r="K41" s="50" t="inlineStr">
+        <is>
+          <t>Not working as expected - see defect</t>
+        </is>
+      </c>
+      <c r="L41" s="50" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="M41" s="50" t="inlineStr">
+        <is>
+          <t>Sahithi Dasari</t>
+        </is>
+      </c>
+      <c r="N41" s="50" t="inlineStr">
+        <is>
+          <t>DEF_02</t>
+        </is>
+      </c>
+      <c r="O41" s="50" t="inlineStr">
+        <is>
+          <t>Automated: test_menu_single_option_message</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="50" t="n">
+        <v>40</v>
+      </c>
+      <c r="C42" s="50" t="inlineStr">
+        <is>
+          <t>TS_Magnus_09</t>
+        </is>
+      </c>
+      <c r="D42" s="50" t="inlineStr">
+        <is>
+          <t>TC_Magnus_40</t>
+        </is>
+      </c>
+      <c r="E42" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F42" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G42" s="50" t="inlineStr">
+        <is>
           <t>Sub menu on mouse hover</t>
         </is>
       </c>
-      <c r="H41" s="50" t="inlineStr">
+      <c r="H42" s="50" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="I41" s="50" t="inlineStr">
+      <c r="I42" s="50" t="inlineStr">
         <is>
           <t>1. Open Sub Menus tab
 2. Hover JAVA
 3. Click Spring</t>
         </is>
       </c>
-      <c r="J41" s="50" t="inlineStr">
+      <c r="J42" s="50" t="inlineStr">
         <is>
           <t>Message mentions Spring</t>
         </is>
       </c>
-      <c r="K41" s="50" t="inlineStr"/>
-      <c r="L41" s="50" t="inlineStr">
+      <c r="K42" s="50" t="n"/>
+      <c r="L42" s="50" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="M41" s="50" t="inlineStr"/>
-      <c r="N41" s="50" t="inlineStr"/>
-      <c r="O41" s="50" t="inlineStr">
+      <c r="M42" s="50" t="n"/>
+      <c r="N42" s="50" t="n"/>
+      <c r="O42" s="50" t="inlineStr">
         <is>
           <t>Automated: test_menu_sub_menu_hover</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="50" t="n">
-        <v>40</v>
-      </c>
-      <c r="C42" s="50" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="50" t="n">
+        <v>41</v>
+      </c>
+      <c r="C43" s="50" t="inlineStr">
         <is>
           <t>TS_Magnus_09</t>
         </is>
       </c>
-      <c r="D42" s="50" t="inlineStr">
-        <is>
-          <t>TC_Magnus_40</t>
-        </is>
-      </c>
-      <c r="E42" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F42" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G42" s="50" t="inlineStr">
+      <c r="D43" s="50" t="inlineStr">
+        <is>
+          <t>TC_Magnus_41</t>
+        </is>
+      </c>
+      <c r="E43" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F43" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G43" s="50" t="inlineStr">
         <is>
           <t>Autocomplete suggestions</t>
         </is>
       </c>
-      <c r="H42" s="50" t="inlineStr">
+      <c r="H43" s="50" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="I42" s="50" t="inlineStr">
+      <c r="I43" s="50" t="inlineStr">
         <is>
           <t>1. Open More &gt; Autocomplete
 2. Type 'Py'
 Test data: Py</t>
         </is>
       </c>
-      <c r="J42" s="50" t="inlineStr">
+      <c r="J43" s="50" t="inlineStr">
         <is>
           <t>'Python' appears in suggestions</t>
         </is>
       </c>
-      <c r="K42" s="50" t="inlineStr"/>
-      <c r="L42" s="50" t="inlineStr">
+      <c r="K43" s="50" t="n"/>
+      <c r="L43" s="50" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="M42" s="50" t="inlineStr"/>
-      <c r="N42" s="50" t="inlineStr"/>
-      <c r="O42" s="50" t="inlineStr">
+      <c r="M43" s="50" t="n"/>
+      <c r="N43" s="50" t="n"/>
+      <c r="O43" s="50" t="inlineStr">
         <is>
           <t>Automated: test_autocomplete_suggestions</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="50" t="n">
-        <v>41</v>
-      </c>
-      <c r="C43" s="50" t="inlineStr">
-        <is>
-          <t>TS_Magnus_09</t>
-        </is>
-      </c>
-      <c r="D43" s="50" t="inlineStr">
-        <is>
-          <t>TC_Magnus_41</t>
-        </is>
-      </c>
-      <c r="E43" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F43" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G43" s="50" t="inlineStr">
-        <is>
-          <t>Collapsible panel expands</t>
-        </is>
-      </c>
-      <c r="H43" s="50" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="I43" s="50" t="inlineStr">
-        <is>
-          <t>1. Open More &gt; Collapsible Content
-2. Click first heading</t>
-        </is>
-      </c>
-      <c r="J43" s="50" t="inlineStr">
-        <is>
-          <t>Panel content expands</t>
-        </is>
-      </c>
-      <c r="K43" s="50" t="inlineStr">
-        <is>
-          <t>Not working as expected - see defect</t>
-        </is>
-      </c>
-      <c r="L43" s="50" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="M43" s="50" t="inlineStr">
-        <is>
-          <t>Sahithi Dasari</t>
-        </is>
-      </c>
-      <c r="N43" s="50" t="inlineStr">
-        <is>
-          <t>DEF_07</t>
-        </is>
-      </c>
-      <c r="O43" s="50" t="inlineStr">
-        <is>
-          <t>Automated: test_collapse_expands_panel | Confirm on screen before submitting</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3876,7 @@
       </c>
       <c r="C44" s="50" t="inlineStr">
         <is>
-          <t>TS_Magnus_10</t>
+          <t>TS_Magnus_09</t>
         </is>
       </c>
       <c r="D44" s="50" t="inlineStr">
@@ -3907,7 +3896,7 @@
       </c>
       <c r="G44" s="50" t="inlineStr">
         <is>
-          <t>Slider value changes</t>
+          <t>Collapsible panel expands</t>
         </is>
       </c>
       <c r="H44" s="50" t="inlineStr">
@@ -3917,26 +3906,26 @@
       </c>
       <c r="I44" s="50" t="inlineStr">
         <is>
-          <t>1. Open More &gt; Slider
-2. Drag the handle</t>
+          <t>1. Open More &gt; Collapsible Content
+2. Click first heading</t>
         </is>
       </c>
       <c r="J44" s="50" t="inlineStr">
         <is>
-          <t>Displayed value changes</t>
-        </is>
-      </c>
-      <c r="K44" s="50" t="inlineStr"/>
+          <t>Panel content expands</t>
+        </is>
+      </c>
+      <c r="K44" s="50" t="n"/>
       <c r="L44" s="50" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="M44" s="50" t="inlineStr"/>
-      <c r="N44" s="50" t="inlineStr"/>
+      <c r="M44" s="50" t="n"/>
+      <c r="N44" s="50" t="n"/>
       <c r="O44" s="50" t="inlineStr">
         <is>
-          <t>Automated: test_slider_drag_changes_value</t>
+          <t>Automated: test_collapse_expands_panel</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3955,7 @@
       </c>
       <c r="G45" s="50" t="inlineStr">
         <is>
-          <t>Tooltip text after click</t>
+          <t>Slider value changes</t>
         </is>
       </c>
       <c r="H45" s="50" t="inlineStr">
@@ -3976,26 +3965,26 @@
       </c>
       <c r="I45" s="50" t="inlineStr">
         <is>
-          <t>1. Open More &gt; Tooltips
-2. Click the button</t>
+          <t>1. Open More &gt; Slider
+2. Drag the handle</t>
         </is>
       </c>
       <c r="J45" s="50" t="inlineStr">
         <is>
-          <t>Tooltip becomes 'Thank you for being here!'</t>
-        </is>
-      </c>
-      <c r="K45" s="50" t="inlineStr"/>
+          <t>Displayed value changes</t>
+        </is>
+      </c>
+      <c r="K45" s="50" t="n"/>
       <c r="L45" s="50" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="M45" s="50" t="inlineStr"/>
-      <c r="N45" s="50" t="inlineStr"/>
+      <c r="M45" s="50" t="n"/>
+      <c r="N45" s="50" t="n"/>
       <c r="O45" s="50" t="inlineStr">
         <is>
-          <t>Automated: test_tooltip_text_changes_after_click</t>
+          <t>Automated: test_slider_drag_changes_value</t>
         </is>
       </c>
     </row>
@@ -4025,83 +4014,142 @@
       </c>
       <c r="G46" s="50" t="inlineStr">
         <is>
+          <t>Tooltip text after click</t>
+        </is>
+      </c>
+      <c r="H46" s="50" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="I46" s="50" t="inlineStr">
+        <is>
+          <t>1. Open More &gt; Tooltips
+2. Click the button</t>
+        </is>
+      </c>
+      <c r="J46" s="50" t="inlineStr">
+        <is>
+          <t>Tooltip becomes 'Thank you for being here!'</t>
+        </is>
+      </c>
+      <c r="K46" s="50" t="n"/>
+      <c r="L46" s="50" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M46" s="50" t="n"/>
+      <c r="N46" s="50" t="n"/>
+      <c r="O46" s="50" t="inlineStr">
+        <is>
+          <t>Automated: test_tooltip_text_changes_after_click</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="50" t="n">
+        <v>45</v>
+      </c>
+      <c r="C47" s="50" t="inlineStr">
+        <is>
+          <t>TS_Magnus_10</t>
+        </is>
+      </c>
+      <c r="D47" s="50" t="inlineStr">
+        <is>
+          <t>TC_Magnus_45</t>
+        </is>
+      </c>
+      <c r="E47" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F47" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G47" s="50" t="inlineStr">
+        <is>
           <t>Alert box</t>
         </is>
       </c>
-      <c r="H46" s="50" t="inlineStr">
+      <c r="H47" s="50" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="I46" s="50" t="inlineStr">
+      <c r="I47" s="50" t="inlineStr">
         <is>
           <t>1. Open More &gt; Popups
 2. Click Alert Box
 3. Click OK</t>
         </is>
       </c>
-      <c r="J46" s="50" t="inlineStr">
+      <c r="J47" s="50" t="inlineStr">
         <is>
           <t>Alert 'This is an alert Box!' shown and closes</t>
         </is>
       </c>
-      <c r="K46" s="50" t="inlineStr">
+      <c r="K47" s="50" t="inlineStr">
         <is>
           <t>Working as expected</t>
         </is>
       </c>
-      <c r="L46" s="50" t="inlineStr">
+      <c r="L47" s="50" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="M46" s="50" t="inlineStr">
+      <c r="M47" s="50" t="inlineStr">
         <is>
           <t>Sahithi Dasari</t>
         </is>
       </c>
-      <c r="N46" s="50" t="inlineStr"/>
-      <c r="O46" s="50" t="inlineStr">
+      <c r="N47" s="50" t="n"/>
+      <c r="O47" s="50" t="inlineStr">
         <is>
           <t>Automated: test_alert_box</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="50" t="n">
-        <v>45</v>
-      </c>
-      <c r="C47" s="50" t="inlineStr">
+    <row r="48">
+      <c r="B48" s="50" t="n">
+        <v>46</v>
+      </c>
+      <c r="C48" s="50" t="inlineStr">
         <is>
           <t>TS_Magnus_10</t>
         </is>
       </c>
-      <c r="D47" s="50" t="inlineStr">
-        <is>
-          <t>TC_Magnus_45</t>
-        </is>
-      </c>
-      <c r="E47" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F47" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G47" s="50" t="inlineStr">
+      <c r="D48" s="50" t="inlineStr">
+        <is>
+          <t>TC_Magnus_46</t>
+        </is>
+      </c>
+      <c r="E48" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F48" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G48" s="50" t="inlineStr">
         <is>
           <t>Prompt box</t>
         </is>
       </c>
-      <c r="H47" s="50" t="inlineStr">
+      <c r="H48" s="50" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="I47" s="50" t="inlineStr">
+      <c r="I48" s="50" t="inlineStr">
         <is>
           <t>1. Click Prompt Box
 2. Type a name
@@ -4109,81 +4157,22 @@
 Test data: Sahithi</t>
         </is>
       </c>
-      <c r="J47" s="50" t="inlineStr">
+      <c r="J48" s="50" t="inlineStr">
         <is>
           <t>Entered name shown on the page</t>
         </is>
       </c>
-      <c r="K47" s="50" t="inlineStr"/>
-      <c r="L47" s="50" t="inlineStr">
+      <c r="K48" s="50" t="n"/>
+      <c r="L48" s="50" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="M47" s="50" t="inlineStr"/>
-      <c r="N47" s="50" t="inlineStr"/>
-      <c r="O47" s="50" t="inlineStr">
+      <c r="M48" s="50" t="n"/>
+      <c r="N48" s="50" t="n"/>
+      <c r="O48" s="50" t="inlineStr">
         <is>
           <t>Automated: test_prompt_box</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="50" t="n">
-        <v>46</v>
-      </c>
-      <c r="C48" s="50" t="inlineStr">
-        <is>
-          <t>TS_Magnus_10</t>
-        </is>
-      </c>
-      <c r="D48" s="50" t="inlineStr">
-        <is>
-          <t>TC_Magnus_46</t>
-        </is>
-      </c>
-      <c r="E48" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F48" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G48" s="50" t="inlineStr">
-        <is>
-          <t>Broken links detected</t>
-        </is>
-      </c>
-      <c r="H48" s="50" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="I48" s="50" t="inlineStr">
-        <is>
-          <t>1. Open More &gt; Links
-2. Check each link's HTTP status</t>
-        </is>
-      </c>
-      <c r="J48" s="50" t="inlineStr">
-        <is>
-          <t>Broken Links tab links return errors; working links return 200</t>
-        </is>
-      </c>
-      <c r="K48" s="50" t="inlineStr"/>
-      <c r="L48" s="50" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M48" s="50" t="inlineStr"/>
-      <c r="N48" s="50" t="inlineStr"/>
-      <c r="O48" s="50" t="inlineStr">
-        <is>
-          <t>Automated: ex5_misc_scenarios.py (broken_links)</t>
         </is>
       </c>
     </row>
@@ -4193,7 +4182,7 @@
       </c>
       <c r="C49" s="50" t="inlineStr">
         <is>
-          <t>TS_Magnus_11</t>
+          <t>TS_Magnus_10</t>
         </is>
       </c>
       <c r="D49" s="50" t="inlineStr">
@@ -4213,7 +4202,7 @@
       </c>
       <c r="G49" s="50" t="inlineStr">
         <is>
-          <t>iFrame Two shows Magnus home</t>
+          <t>Broken links detected</t>
         </is>
       </c>
       <c r="H49" s="50" t="inlineStr">
@@ -4223,38 +4212,26 @@
       </c>
       <c r="I49" s="50" t="inlineStr">
         <is>
-          <t>1. Open More &gt; iFrames
-2. Switch to Frame Two</t>
+          <t>1. Open More &gt; Links
+2. Check each link's HTTP status</t>
         </is>
       </c>
       <c r="J49" s="50" t="inlineStr">
         <is>
-          <t>Magnus menu visible inside the frame</t>
-        </is>
-      </c>
-      <c r="K49" s="50" t="inlineStr">
-        <is>
-          <t>Not working as expected - see defect</t>
-        </is>
-      </c>
+          <t>Broken Links tab links return errors; working links return 200</t>
+        </is>
+      </c>
+      <c r="K49" s="50" t="n"/>
       <c r="L49" s="50" t="inlineStr">
         <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="M49" s="50" t="inlineStr">
-        <is>
-          <t>Sahithi Dasari</t>
-        </is>
-      </c>
-      <c r="N49" s="50" t="inlineStr">
-        <is>
-          <t>DEF_06</t>
-        </is>
-      </c>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M49" s="50" t="n"/>
+      <c r="N49" s="50" t="n"/>
       <c r="O49" s="50" t="inlineStr">
         <is>
-          <t>Automated: test_iframe_two_shows_home_page | Confirm on screen before submitting</t>
+          <t>Automated: ex5_misc_scenarios.py (broken_links)</t>
         </is>
       </c>
     </row>
@@ -4284,93 +4261,93 @@
       </c>
       <c r="G50" s="50" t="inlineStr">
         <is>
+          <t>iFrame Two shows Magnus home</t>
+        </is>
+      </c>
+      <c r="H50" s="50" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="I50" s="50" t="inlineStr">
+        <is>
+          <t>1. Open More &gt; iFrames
+2. Switch to Frame Two</t>
+        </is>
+      </c>
+      <c r="J50" s="50" t="inlineStr">
+        <is>
+          <t>Magnus menu visible inside the frame</t>
+        </is>
+      </c>
+      <c r="K50" s="50" t="n"/>
+      <c r="L50" s="50" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M50" s="50" t="n"/>
+      <c r="N50" s="50" t="n"/>
+      <c r="O50" s="50" t="inlineStr">
+        <is>
+          <t>Automated: test_iframe_two_shows_home_page</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="50" t="n">
+        <v>49</v>
+      </c>
+      <c r="C51" s="50" t="inlineStr">
+        <is>
+          <t>TS_Magnus_11</t>
+        </is>
+      </c>
+      <c r="D51" s="50" t="inlineStr">
+        <is>
+          <t>TC_Magnus_49</t>
+        </is>
+      </c>
+      <c r="E51" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F51" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G51" s="50" t="inlineStr">
+        <is>
           <t>Upload only image files</t>
         </is>
       </c>
-      <c r="H50" s="50" t="inlineStr">
+      <c r="H51" s="50" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="I50" s="50" t="inlineStr">
+      <c r="I51" s="50" t="inlineStr">
         <is>
           <t>1. Open More &gt; Images
 2. Choose a .txt file
 Test data: notes.txt</t>
         </is>
       </c>
-      <c r="J50" s="50" t="inlineStr">
+      <c r="J51" s="50" t="inlineStr">
         <is>
           <t>Error: only jpg, jpeg, png, gif or bmp allowed</t>
         </is>
       </c>
-      <c r="K50" s="50" t="inlineStr"/>
-      <c r="L50" s="50" t="inlineStr">
+      <c r="K51" s="50" t="n"/>
+      <c r="L51" s="50" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="M50" s="50" t="inlineStr"/>
-      <c r="N50" s="50" t="inlineStr"/>
-      <c r="O50" s="50" t="inlineStr">
-        <is>
-          <t>Manual test</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="50" t="n">
-        <v>49</v>
-      </c>
-      <c r="C51" s="50" t="inlineStr">
-        <is>
-          <t>TS_Magnus_12</t>
-        </is>
-      </c>
-      <c r="D51" s="50" t="inlineStr">
-        <is>
-          <t>TC_Magnus_49</t>
-        </is>
-      </c>
-      <c r="E51" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F51" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G51" s="50" t="inlineStr">
-        <is>
-          <t>Change Password - empty fields</t>
-        </is>
-      </c>
-      <c r="H51" s="50" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="I51" s="50" t="inlineStr">
-        <is>
-          <t>1. Open Settings &gt; Change Password
-2. Click Change Password</t>
-        </is>
-      </c>
-      <c r="J51" s="50" t="inlineStr">
-        <is>
-          <t>Required messages for old, new and confirm password</t>
-        </is>
-      </c>
-      <c r="K51" s="50" t="inlineStr"/>
-      <c r="L51" s="50" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M51" s="50" t="inlineStr"/>
-      <c r="N51" s="50" t="inlineStr"/>
+      <c r="M51" s="50" t="n"/>
+      <c r="N51" s="50" t="n"/>
       <c r="O51" s="50" t="inlineStr">
         <is>
           <t>Manual test</t>
@@ -4403,15 +4380,74 @@
       </c>
       <c r="G52" s="50" t="inlineStr">
         <is>
+          <t>Change Password - empty fields</t>
+        </is>
+      </c>
+      <c r="H52" s="50" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="I52" s="50" t="inlineStr">
+        <is>
+          <t>1. Open Settings &gt; Change Password
+2. Click Change Password</t>
+        </is>
+      </c>
+      <c r="J52" s="50" t="inlineStr">
+        <is>
+          <t>Required messages for old, new and confirm password</t>
+        </is>
+      </c>
+      <c r="K52" s="50" t="n"/>
+      <c r="L52" s="50" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M52" s="50" t="n"/>
+      <c r="N52" s="50" t="n"/>
+      <c r="O52" s="50" t="inlineStr">
+        <is>
+          <t>Manual test</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="50" t="n">
+        <v>51</v>
+      </c>
+      <c r="C53" s="50" t="inlineStr">
+        <is>
+          <t>TS_Magnus_12</t>
+        </is>
+      </c>
+      <c r="D53" s="50" t="inlineStr">
+        <is>
+          <t>TC_Magnus_51</t>
+        </is>
+      </c>
+      <c r="E53" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F53" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G53" s="50" t="inlineStr">
+        <is>
           <t>Change Password - confirm does not match</t>
         </is>
       </c>
-      <c r="H52" s="50" t="inlineStr">
+      <c r="H53" s="50" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="I52" s="50" t="inlineStr">
+      <c r="I53" s="50" t="inlineStr">
         <is>
           <t>1. Enter old password
 2. Enter different new and confirm values
@@ -4419,20 +4455,20 @@
 Test data: new: Abc@1234 / confirm: Xyz@1234</t>
         </is>
       </c>
-      <c r="J52" s="50" t="inlineStr">
+      <c r="J53" s="50" t="inlineStr">
         <is>
           <t>'Confirm password and password must be same.' Do NOT submit a valid change - it is a shared account</t>
         </is>
       </c>
-      <c r="K52" s="50" t="inlineStr"/>
-      <c r="L52" s="50" t="inlineStr">
+      <c r="K53" s="50" t="n"/>
+      <c r="L53" s="50" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="M52" s="50" t="inlineStr"/>
-      <c r="N52" s="50" t="inlineStr"/>
-      <c r="O52" s="50" t="inlineStr">
+      <c r="M53" s="50" t="n"/>
+      <c r="N53" s="50" t="n"/>
+      <c r="O53" s="50" t="inlineStr">
         <is>
           <t>Manual test</t>
         </is>
